--- a/artfynd/A 32276-2026 artfynd.xlsx
+++ b/artfynd/A 32276-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135791503</v>
       </c>
       <c r="B2" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32276-2026 artfynd.xlsx
+++ b/artfynd/A 32276-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135791503</v>
       </c>
       <c r="B2" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32276-2026 artfynd.xlsx
+++ b/artfynd/A 32276-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>135791503</v>
+        <v>136189262</v>
       </c>
       <c r="B2" t="n">
-        <v>80559</v>
+        <v>92065</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,38 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bryngelhögen, Jmt</t>
+          <t>Norrbodstugan, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>474235</v>
+        <v>474138</v>
       </c>
       <c r="R2" t="n">
-        <v>6920986</v>
+        <v>6921090</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,17 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,24 +775,2631 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136189262</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>135791503</v>
+      </c>
+      <c r="B3" t="n">
+        <v>80559</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Bryngelhögen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>474235</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6920986</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Rätan</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/135791503</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>136189253</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Norrbodstugan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>474159</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6921114</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Rätan</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Tall Färska och äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136189253</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>136189256</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Norrbodstugan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>474175</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6921123</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Rätan</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136189256</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136189259</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Norrbodstugan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>474126</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6921158</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Rätan</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136189259</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>136189260</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Norrbodstugan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>474125</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6921152</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Rätan</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136189260</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136189263</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Norrbodstugan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>474138</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6921083</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Rätan</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136189263</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136189265</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Norrbodstugan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>474130</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6921080</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Rätan</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136189265</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>136189266</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Norrbodstugan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>474133</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6921082</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Rätan</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136189266</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>136189268</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Norrbodstugan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>474113</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6921091</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Rätan</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136189268</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>136189270</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Norrbodstugan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>474112</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6920975</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Rätan</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136189270</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>136189272</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Norrbodstugan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>474151</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6920984</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Rätan</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På tall Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136189272</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>136189274</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Norrbodstugan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>474171</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6921059</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Rätan</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136189274</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>136189277</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Norrbodstugan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>474174</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6921004</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Rätan</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136189277</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>136189278</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Norrbodstugan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>474179</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6920958</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Rätan</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136189278</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>136189279</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Norrbodstugan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>474185</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6920953</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Rätan</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136189279</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>136189267</v>
+      </c>
+      <c r="B18" t="n">
+        <v>58086</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Norrbodstugan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>474131</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6921083</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Rätan</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136189267</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>136189248</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99294</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Norrbodstugan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>474199</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6920996</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Rätan</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136189248</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>136189249</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99294</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Norrbodstugan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>474189</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6920992</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Rätan</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136189249</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>136189251</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99294</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Norrbodstugan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>474198</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6921045</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Rätan</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136189251</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>136189252</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99294</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Norrbodstugan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>474200</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6921059</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Rätan</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136189252</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>136189258</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99294</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Norrbodstugan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>474125</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6921161</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Rätan</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136189258</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>136189250</v>
+      </c>
+      <c r="B24" t="n">
+        <v>110039</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>221184</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Torta</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lactuca alpina</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Norrbodstugan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>474198</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6921006</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Rätan</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136189250</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 32276-2026 artfynd.xlsx
+++ b/artfynd/A 32276-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136189262</v>
       </c>
       <c r="B2" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>136189248</v>
       </c>
       <c r="B19" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         <v>136189249</v>
       </c>
       <c r="B20" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>136189251</v>
       </c>
       <c r="B21" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         <v>136189252</v>
       </c>
       <c r="B22" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3156,7 +3156,7 @@
         <v>136189258</v>
       </c>
       <c r="B23" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>136189250</v>
       </c>
       <c r="B24" t="n">
-        <v>110039</v>
+        <v>110040</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 32276-2026 artfynd.xlsx
+++ b/artfynd/A 32276-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136189262</v>
       </c>
       <c r="B2" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135791503</v>
       </c>
       <c r="B3" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>136189253</v>
       </c>
       <c r="B4" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136189256</v>
       </c>
       <c r="B5" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>136189259</v>
       </c>
       <c r="B6" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>136189260</v>
       </c>
       <c r="B7" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v>136189263</v>
       </c>
       <c r="B8" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>136189265</v>
       </c>
       <c r="B9" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>136189266</v>
       </c>
       <c r="B10" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>136189268</v>
       </c>
       <c r="B11" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>136189270</v>
       </c>
       <c r="B12" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
         <v>136189272</v>
       </c>
       <c r="B13" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
         <v>136189274</v>
       </c>
       <c r="B14" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>136189277</v>
       </c>
       <c r="B15" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>136189278</v>
       </c>
       <c r="B16" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
         <v>136189279</v>
       </c>
       <c r="B17" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>136189267</v>
       </c>
       <c r="B18" t="n">
-        <v>58086</v>
+        <v>58087</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>136189248</v>
       </c>
       <c r="B19" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         <v>136189249</v>
       </c>
       <c r="B20" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>136189251</v>
       </c>
       <c r="B21" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         <v>136189252</v>
       </c>
       <c r="B22" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3156,7 +3156,7 @@
         <v>136189258</v>
       </c>
       <c r="B23" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>136189250</v>
       </c>
       <c r="B24" t="n">
-        <v>110040</v>
+        <v>110041</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 32276-2026 artfynd.xlsx
+++ b/artfynd/A 32276-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136189262</v>
       </c>
       <c r="B2" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135791503</v>
       </c>
       <c r="B3" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>136189253</v>
       </c>
       <c r="B4" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136189256</v>
       </c>
       <c r="B5" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>136189259</v>
       </c>
       <c r="B6" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>136189260</v>
       </c>
       <c r="B7" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v>136189263</v>
       </c>
       <c r="B8" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>136189265</v>
       </c>
       <c r="B9" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>136189266</v>
       </c>
       <c r="B10" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>136189268</v>
       </c>
       <c r="B11" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>136189270</v>
       </c>
       <c r="B12" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
         <v>136189272</v>
       </c>
       <c r="B13" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
         <v>136189274</v>
       </c>
       <c r="B14" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>136189277</v>
       </c>
       <c r="B15" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>136189278</v>
       </c>
       <c r="B16" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
         <v>136189279</v>
       </c>
       <c r="B17" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>136189267</v>
       </c>
       <c r="B18" t="n">
-        <v>58087</v>
+        <v>58091</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>136189248</v>
       </c>
       <c r="B19" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         <v>136189249</v>
       </c>
       <c r="B20" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>136189251</v>
       </c>
       <c r="B21" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         <v>136189252</v>
       </c>
       <c r="B22" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3156,7 +3156,7 @@
         <v>136189258</v>
       </c>
       <c r="B23" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>136189250</v>
       </c>
       <c r="B24" t="n">
-        <v>110041</v>
+        <v>110047</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 32276-2026 artfynd.xlsx
+++ b/artfynd/A 32276-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136189262</v>
       </c>
       <c r="B2" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135791503</v>
       </c>
       <c r="B3" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>136189253</v>
       </c>
       <c r="B4" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136189256</v>
       </c>
       <c r="B5" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>136189259</v>
       </c>
       <c r="B6" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>136189260</v>
       </c>
       <c r="B7" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v>136189263</v>
       </c>
       <c r="B8" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>136189265</v>
       </c>
       <c r="B9" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>136189266</v>
       </c>
       <c r="B10" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>136189268</v>
       </c>
       <c r="B11" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>136189270</v>
       </c>
       <c r="B12" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
         <v>136189272</v>
       </c>
       <c r="B13" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
         <v>136189274</v>
       </c>
       <c r="B14" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>136189277</v>
       </c>
       <c r="B15" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>136189278</v>
       </c>
       <c r="B16" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
         <v>136189279</v>
       </c>
       <c r="B17" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>136189267</v>
       </c>
       <c r="B18" t="n">
-        <v>58091</v>
+        <v>58092</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>136189248</v>
       </c>
       <c r="B19" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         <v>136189249</v>
       </c>
       <c r="B20" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>136189251</v>
       </c>
       <c r="B21" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         <v>136189252</v>
       </c>
       <c r="B22" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3156,7 +3156,7 @@
         <v>136189258</v>
       </c>
       <c r="B23" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>136189250</v>
       </c>
       <c r="B24" t="n">
-        <v>110047</v>
+        <v>110048</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 32276-2026 artfynd.xlsx
+++ b/artfynd/A 32276-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136189262</v>
       </c>
       <c r="B2" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135791503</v>
       </c>
       <c r="B3" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>136189248</v>
       </c>
       <c r="B19" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         <v>136189249</v>
       </c>
       <c r="B20" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>136189251</v>
       </c>
       <c r="B21" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         <v>136189252</v>
       </c>
       <c r="B22" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3156,7 +3156,7 @@
         <v>136189258</v>
       </c>
       <c r="B23" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>136189250</v>
       </c>
       <c r="B24" t="n">
-        <v>110048</v>
+        <v>110059</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 32276-2026 artfynd.xlsx
+++ b/artfynd/A 32276-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136189262</v>
       </c>
       <c r="B2" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135791503</v>
       </c>
       <c r="B3" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>136189253</v>
       </c>
       <c r="B4" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136189256</v>
       </c>
       <c r="B5" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>136189259</v>
       </c>
       <c r="B6" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>136189260</v>
       </c>
       <c r="B7" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v>136189263</v>
       </c>
       <c r="B8" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>136189265</v>
       </c>
       <c r="B9" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>136189266</v>
       </c>
       <c r="B10" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>136189268</v>
       </c>
       <c r="B11" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>136189270</v>
       </c>
       <c r="B12" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
         <v>136189272</v>
       </c>
       <c r="B13" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
         <v>136189274</v>
       </c>
       <c r="B14" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>136189277</v>
       </c>
       <c r="B15" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>136189278</v>
       </c>
       <c r="B16" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
         <v>136189279</v>
       </c>
       <c r="B17" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>136189267</v>
       </c>
       <c r="B18" t="n">
-        <v>58092</v>
+        <v>58097</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>136189248</v>
       </c>
       <c r="B19" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         <v>136189249</v>
       </c>
       <c r="B20" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>136189251</v>
       </c>
       <c r="B21" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         <v>136189252</v>
       </c>
       <c r="B22" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3156,7 +3156,7 @@
         <v>136189258</v>
       </c>
       <c r="B23" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>136189250</v>
       </c>
       <c r="B24" t="n">
-        <v>110059</v>
+        <v>110072</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 32276-2026 artfynd.xlsx
+++ b/artfynd/A 32276-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136189262</v>
       </c>
       <c r="B2" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>136189248</v>
       </c>
       <c r="B19" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         <v>136189249</v>
       </c>
       <c r="B20" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>136189251</v>
       </c>
       <c r="B21" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         <v>136189252</v>
       </c>
       <c r="B22" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3156,7 +3156,7 @@
         <v>136189258</v>
       </c>
       <c r="B23" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>136189250</v>
       </c>
       <c r="B24" t="n">
-        <v>110072</v>
+        <v>110073</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 32276-2026 artfynd.xlsx
+++ b/artfynd/A 32276-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136189262</v>
       </c>
       <c r="B2" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>136189253</v>
       </c>
       <c r="B4" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136189256</v>
       </c>
       <c r="B5" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>136189259</v>
       </c>
       <c r="B6" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>136189260</v>
       </c>
       <c r="B7" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v>136189263</v>
       </c>
       <c r="B8" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>136189265</v>
       </c>
       <c r="B9" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>136189266</v>
       </c>
       <c r="B10" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>136189268</v>
       </c>
       <c r="B11" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>136189270</v>
       </c>
       <c r="B12" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
         <v>136189272</v>
       </c>
       <c r="B13" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
         <v>136189274</v>
       </c>
       <c r="B14" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>136189277</v>
       </c>
       <c r="B15" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>136189278</v>
       </c>
       <c r="B16" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
         <v>136189279</v>
       </c>
       <c r="B17" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>136189267</v>
       </c>
       <c r="B18" t="n">
-        <v>58097</v>
+        <v>58110</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>136189248</v>
       </c>
       <c r="B19" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         <v>136189249</v>
       </c>
       <c r="B20" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>136189251</v>
       </c>
       <c r="B21" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         <v>136189252</v>
       </c>
       <c r="B22" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3156,7 +3156,7 @@
         <v>136189258</v>
       </c>
       <c r="B23" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>136189250</v>
       </c>
       <c r="B24" t="n">
-        <v>110073</v>
+        <v>110086</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 32276-2026 artfynd.xlsx
+++ b/artfynd/A 32276-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136189262</v>
       </c>
       <c r="B2" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>136189248</v>
       </c>
       <c r="B19" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         <v>136189249</v>
       </c>
       <c r="B20" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>136189251</v>
       </c>
       <c r="B21" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         <v>136189252</v>
       </c>
       <c r="B22" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3156,7 +3156,7 @@
         <v>136189258</v>
       </c>
       <c r="B23" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>136189250</v>
       </c>
       <c r="B24" t="n">
-        <v>110086</v>
+        <v>110087</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
